--- a/sources/yoshimitsu_step3.xlsx
+++ b/sources/yoshimitsu_step3.xlsx
@@ -685,6 +685,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>354a3fa8-57b9-4015-af73-fbbd2a144a43</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
           <t>354a3fa8-57b9-4015-af73-fbbd2a144a43</t>
@@ -722,6 +727,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>20aa9f1d-6b31-434f-844f-26957fc46e7e</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
           <t>20aa9f1d-6b31-434f-844f-26957fc46e7e</t>
@@ -757,6 +767,11 @@
       <c r="K8" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>7e99b815-adc2-430a-a808-4fc52a37e967</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -6722,6 +6737,11 @@
           <t>hmmhhLm[!][!]!</t>
         </is>
       </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>7a24210e-7ae9-446c-a303-2ad7eba2ac12</t>
+        </is>
+      </c>
       <c r="O134" t="inlineStr">
         <is>
           <t>7a24210e-7ae9-446c-a303-2ad7eba2ac12</t>
@@ -6749,6 +6769,11 @@
           <t>hmmhmmmm[!]!</t>
         </is>
       </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>e7491c61-b40c-4c01-87b6-9b84db2d350e</t>
+        </is>
+      </c>
       <c r="O135" t="inlineStr">
         <is>
           <t>e7491c61-b40c-4c01-87b6-9b84db2d350e</t>
@@ -6776,6 +6801,11 @@
           <t>hhmhhLm[!][!]!</t>
         </is>
       </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>51b32f66-b200-49c0-ad4b-c52c71e51bcd</t>
+        </is>
+      </c>
       <c r="O136" t="inlineStr">
         <is>
           <t>51b32f66-b200-49c0-ad4b-c52c71e51bcd</t>
@@ -6803,6 +6833,11 @@
           <t>hmmhhLmm</t>
         </is>
       </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>11bf5f22-1ce6-4a60-a66b-d9ef064953bb</t>
+        </is>
+      </c>
       <c r="O137" t="inlineStr">
         <is>
           <t>11bf5f22-1ce6-4a60-a66b-d9ef064953bb</t>
@@ -6830,6 +6865,11 @@
           <t>hhmhhLmm</t>
         </is>
       </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>9b6d5b1e-d48e-46f1-b1c7-21d5b7e3d2e1</t>
+        </is>
+      </c>
       <c r="O138" t="inlineStr">
         <is>
           <t>9b6d5b1e-d48e-46f1-b1c7-21d5b7e3d2e1</t>
@@ -6857,6 +6897,11 @@
           <t>hhmh!</t>
         </is>
       </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>1d6b4525-e2f5-45b8-b095-3e41e4cec56b</t>
+        </is>
+      </c>
       <c r="O139" t="inlineStr">
         <is>
           <t>1d6b4525-e2f5-45b8-b095-3e41e4cec56b</t>
@@ -6882,6 +6927,11 @@
       <c r="I140" t="inlineStr">
         <is>
           <t>hhmh!</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>d39521f6-f2ff-4975-8663-4aac08ebeffc</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
